--- a/Sprints/Sprint-(-1)/CS 160 - Team 4 Project Survey Responses.xlsx
+++ b/Sprints/Sprint-(-1)/CS 160 - Team 4 Project Survey Responses.xlsx
@@ -1,13 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion rupBuild="9303" lowestEdited="5" lastEdited="5" appName="xl"/>
   <workbookPr/>
+  <bookViews>
+    <workbookView xWindow="480" yWindow="60" windowWidth="18195" windowHeight="8505" activeTab="0"/>
+  </bookViews>
   <sheets>
-    <sheet state="visible" name="Form Responses 1" sheetId="1" r:id="rId5"/>
-    <sheet state="visible" name="Sheet1" sheetId="2" r:id="rId6"/>
+    <sheet r:id="rId1" sheetId="1" name="Form Responses 1"/>
+    <sheet r:id="rId2" sheetId="2" name="Sheet1"/>
   </sheets>
-  <definedNames/>
-  <calcPr/>
+  <calcPr fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
@@ -395,21 +398,23 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" mc:Ignorable="x14ac">
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="m/d/yyyy h:mm:ss"/>
   </numFmts>
-  <fonts count="2">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
-      <sz val="10.0"/>
-      <color rgb="FF000000"/>
-      <name val="Arial"/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <color theme="1"/>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
       <name val="Arial"/>
-      <scheme val="minor"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="2">
@@ -417,118 +422,71 @@
       <patternFill patternType="none"/>
     </fill>
     <fill>
-      <patternFill patternType="lightGray"/>
+      <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
-    <border/>
+  <borders count="2">
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
+  <cellXfs count="9">
+    <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0"/>
+    <xf xfId="0" numFmtId="164" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="1" applyFont="1" fillId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment horizontal="left" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
+    <xf xfId="0" numFmtId="0" borderId="1" applyBorder="1" fontId="1" applyFont="1" fillId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="164" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
+    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="1" applyFont="1" fillId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
+    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="1" applyFont="1" fillId="0" applyAlignment="1">
+      <alignment horizontal="right"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="164" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
+    <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0" applyAlignment="1">
+      <alignment horizontal="general"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
+    <xf xfId="0" numFmtId="164" applyNumberFormat="1" borderId="0" fontId="0" fillId="0" applyAlignment="1">
+      <alignment horizontal="general"/>
+    </xf>
+    <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0" applyAlignment="1">
+      <alignment horizontal="general"/>
+    </xf>
+    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="0" fontId="0" fillId="0" applyAlignment="1">
+      <alignment horizontal="right"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle xfId="0" name="Normal" builtinId="0"/>
+    <cellStyle xfId="0" builtinId="0" name="Normal"/>
   </cellStyles>
-  <dxfs count="5">
-    <dxf>
-      <font/>
-      <fill>
-        <patternFill patternType="none"/>
-      </fill>
-      <border/>
-    </dxf>
-    <dxf>
-      <font/>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF5B3F86"/>
-          <bgColor rgb="FF5B3F86"/>
-        </patternFill>
-      </fill>
-      <border/>
-    </dxf>
-    <dxf>
-      <font/>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-      <border/>
-    </dxf>
-    <dxf>
-      <font/>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-      <border/>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color rgb="FF5B3F86"/>
-        </left>
-        <right style="thin">
-          <color rgb="FF5B3F86"/>
-        </right>
-        <top style="thin">
-          <color rgb="FF5B3F86"/>
-        </top>
-        <bottom style="thin">
-          <color rgb="FF5B3F86"/>
-        </bottom>
-      </border>
-    </dxf>
-  </dxfs>
-  <tableStyles count="1">
-    <tableStyle count="4" pivot="0" name="Form Responses 1-style">
-      <tableStyleElement dxfId="1" type="headerRow"/>
-      <tableStyleElement dxfId="2" type="firstRowStripe"/>
-      <tableStyleElement dxfId="3" type="secondRowStripe"/>
-      <tableStyleElement dxfId="4" size="0" type="wholeTable"/>
-    </tableStyle>
-  </tableStyles>
+  <dxfs count="0"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14ac:slicerStyles xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
-<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
-</file>
-
-<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<x18tc:personList xmlns:x18tc="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments"/>
-</file>
-
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" ref="A1:AF14" displayName="Form_Responses" name="Form_Responses" id="1">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" ref="A1:AF14" displayName="Form_Responses" name="Form_Responses" id="1" totalsRowShown="0">
+  <autoFilter ref="A1:AF14"/>
   <tableColumns count="32">
     <tableColumn name="Timestamp" id="1"/>
     <tableColumn name="Student name" id="2"/>
@@ -563,19 +521,19 @@
     <tableColumn name="18. If the voice assistant could not understand the user after several attempts, what should it do?" id="31"/>
     <tableColumn name="19. Is there another feature, concern, or suggestion that you think our team should consider?" id="32"/>
   </tableColumns>
-  <tableStyleInfo name="Form Responses 1-style" showColumnStripes="0" showFirstColumn="1" showLastColumn="1" showRowStripes="1"/>
+  <tableStyleInfo name="TableStyleLight1" showColumnStripes="0" showRowStripes="1" showLastColumn="1" showFirstColumn="1"/>
 </table>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheets">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
-    <a:clrScheme name="Sheets">
+    <a:clrScheme name="Office">
       <a:dk1>
-        <a:srgbClr val="000000"/>
+        <a:sysClr lastClr="000000" val="windowText"/>
       </a:dk1>
       <a:lt1>
-        <a:srgbClr val="FFFFFF"/>
+        <a:sysClr lastClr="FFFFFF" val="window"/>
       </a:lt1>
       <a:dk2>
         <a:srgbClr val="000000"/>
@@ -602,22 +560,82 @@
         <a:srgbClr val="46BDC6"/>
       </a:accent6>
       <a:hlink>
-        <a:srgbClr val="1155CC"/>
+        <a:srgbClr val="0000FF"/>
       </a:hlink>
       <a:folHlink>
-        <a:srgbClr val="1155CC"/>
+        <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Sheets">
+    <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Arial"/>
-        <a:ea typeface="Arial"/>
-        <a:cs typeface="Arial"/>
+        <a:latin typeface="Cambria"/>
+        <a:ea typeface=""/>
+        <a:cs typeface=""/>
+        <a:font typeface="ＭＳ Ｐゴシック" script="Jpan"/>
+        <a:font typeface="맑은 고딕" script="Hang"/>
+        <a:font typeface="宋体" script="Hans"/>
+        <a:font typeface="新細明體" script="Hant"/>
+        <a:font typeface="Times New Roman" script="Arab"/>
+        <a:font typeface="Times New Roman" script="Hebr"/>
+        <a:font typeface="Tahoma" script="Thai"/>
+        <a:font typeface="Nyala" script="Ethi"/>
+        <a:font typeface="Vrinda" script="Beng"/>
+        <a:font typeface="Shruti" script="Gujr"/>
+        <a:font typeface="MoolBoran" script="Khmr"/>
+        <a:font typeface="Tunga" script="Knda"/>
+        <a:font typeface="Raavi" script="Guru"/>
+        <a:font typeface="Euphemia" script="Cans"/>
+        <a:font typeface="Plantagenet Cherokee" script="Cher"/>
+        <a:font typeface="Microsoft Yi Baiti" script="Yiii"/>
+        <a:font typeface="Microsoft Himalaya" script="Tibt"/>
+        <a:font typeface="MV Boli" script="Thaa"/>
+        <a:font typeface="Mangal" script="Deva"/>
+        <a:font typeface="Gautami" script="Telu"/>
+        <a:font typeface="Latha" script="Taml"/>
+        <a:font typeface="Estrangelo Edessa" script="Syrc"/>
+        <a:font typeface="Kalinga" script="Orya"/>
+        <a:font typeface="Kartika" script="Mlym"/>
+        <a:font typeface="DokChampa" script="Laoo"/>
+        <a:font typeface="Iskoola Pota" script="Sinh"/>
+        <a:font typeface="Mongolian Baiti" script="Mong"/>
+        <a:font typeface="Times New Roman" script="Viet"/>
+        <a:font typeface="Microsoft Uighur" script="Uigh"/>
+        <a:font typeface="Sylfaen" script="Geor"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Arial"/>
-        <a:ea typeface="Arial"/>
-        <a:cs typeface="Arial"/>
+        <a:latin typeface="Calibri"/>
+        <a:ea typeface=""/>
+        <a:cs typeface=""/>
+        <a:font typeface="ＭＳ Ｐゴシック" script="Jpan"/>
+        <a:font typeface="맑은 고딕" script="Hang"/>
+        <a:font typeface="宋体" script="Hans"/>
+        <a:font typeface="新細明體" script="Hant"/>
+        <a:font typeface="Arial" script="Arab"/>
+        <a:font typeface="Arial" script="Hebr"/>
+        <a:font typeface="Tahoma" script="Thai"/>
+        <a:font typeface="Nyala" script="Ethi"/>
+        <a:font typeface="Vrinda" script="Beng"/>
+        <a:font typeface="Shruti" script="Gujr"/>
+        <a:font typeface="DaunPenh" script="Khmr"/>
+        <a:font typeface="Tunga" script="Knda"/>
+        <a:font typeface="Raavi" script="Guru"/>
+        <a:font typeface="Euphemia" script="Cans"/>
+        <a:font typeface="Plantagenet Cherokee" script="Cher"/>
+        <a:font typeface="Microsoft Yi Baiti" script="Yiii"/>
+        <a:font typeface="Microsoft Himalaya" script="Tibt"/>
+        <a:font typeface="MV Boli" script="Thaa"/>
+        <a:font typeface="Mangal" script="Deva"/>
+        <a:font typeface="Gautami" script="Telu"/>
+        <a:font typeface="Latha" script="Taml"/>
+        <a:font typeface="Estrangelo Edessa" script="Syrc"/>
+        <a:font typeface="Kalinga" script="Orya"/>
+        <a:font typeface="Kartika" script="Mlym"/>
+        <a:font typeface="DokChampa" script="Laoo"/>
+        <a:font typeface="Iskoola Pota" script="Sinh"/>
+        <a:font typeface="Mongolian Baiti" script="Mong"/>
+        <a:font typeface="Arial" script="Viet"/>
+        <a:font typeface="Microsoft Uighur" script="Uigh"/>
+        <a:font typeface="Sylfaen" script="Geor"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -629,1514 +647,1581 @@
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:lumMod val="110000"/>
-                <a:satMod val="105000"/>
-                <a:tint val="67000"/>
+                <a:tint val="50000"/>
+                <a:satMod val="300000"/>
               </a:schemeClr>
             </a:gs>
-            <a:gs pos="50000">
+            <a:gs pos="35000">
               <a:schemeClr val="phClr">
-                <a:lumMod val="105000"/>
-                <a:satMod val="103000"/>
-                <a:tint val="73000"/>
+                <a:tint val="37000"/>
+                <a:satMod val="300000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:lumMod val="105000"/>
-                <a:satMod val="109000"/>
-                <a:tint val="81000"/>
+                <a:satMod val="350000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="5400000" scaled="0"/>
+          <a:lin scaled="1" ang="16200000"/>
         </a:gradFill>
         <a:gradFill rotWithShape="1">
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:satMod val="103000"/>
-                <a:lumMod val="102000"/>
-                <a:tint val="94000"/>
+                <a:tint val="51000"/>
+                <a:satMod val="130000"/>
               </a:schemeClr>
             </a:gs>
-            <a:gs pos="50000">
+            <a:gs pos="80000">
               <a:schemeClr val="phClr">
-                <a:satMod val="110000"/>
-                <a:lumMod val="100000"/>
-                <a:shade val="100000"/>
+                <a:tint val="15000"/>
+                <a:satMod val="130000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:lumMod val="99000"/>
-                <a:satMod val="120000"/>
-                <a:shade val="78000"/>
+                <a:tint val="94000"/>
+                <a:satMod val="135000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="5400000" scaled="0"/>
+          <a:lin scaled="1" ang="16200000"/>
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
-        <a:ln w="6350" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln algn="ctr" cmpd="sng" cap="flat" w="9525">
+          <a:solidFill>
+            <a:schemeClr val="phClr">
+              <a:shade val="9500"/>
+              <a:satMod val="105000"/>
+            </a:schemeClr>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+        </a:ln>
+        <a:ln algn="ctr" cmpd="sng" cap="flat" w="25400">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
         </a:ln>
-        <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln algn="ctr" cmpd="sng" cap="flat" w="38100">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
-        </a:ln>
-        <a:ln w="19050" cap="flat" cmpd="sng" algn="ctr">
-          <a:solidFill>
-            <a:schemeClr val="phClr"/>
-          </a:solidFill>
-          <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
         </a:ln>
       </a:lnStyleLst>
       <a:effectStyleLst>
         <a:effectStyle>
-          <a:effectLst/>
-        </a:effectStyle>
-        <a:effectStyle>
-          <a:effectLst/>
+          <a:effectLst>
+            <a:outerShdw dir="5400000" rotWithShape="0" dist="23000" blurRad="40000">
+              <a:srgbClr val="000000">
+                <a:alpha val="38000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
         </a:effectStyle>
         <a:effectStyle>
           <a:effectLst>
-            <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
+            <a:outerShdw dir="5400000" rotWithShape="0" dist="23000" blurRad="40000">
               <a:srgbClr val="000000">
-                <a:alpha val="63000"/>
+                <a:alpha val="35000"/>
               </a:srgbClr>
             </a:outerShdw>
           </a:effectLst>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst>
+            <a:outerShdw dir="5400000" rotWithShape="0" dist="23000" blurRad="40000">
+              <a:srgbClr val="000000">
+                <a:alpha val="35000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
+          <a:scene3d>
+            <a:camera prst="orthographicFront">
+              <a:rot rev="0" lon="0" lat="0"/>
+            </a:camera>
+            <a:lightRig dir="t" rig="threePt">
+              <a:rot rev="1200000" lon="0" lat="0"/>
+            </a:lightRig>
+          </a:scene3d>
+          <a:sp3d>
+            <a:bevelT w="63500" h="25400"/>
+          </a:sp3d>
         </a:effectStyle>
       </a:effectStyleLst>
       <a:bgFillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
         </a:solidFill>
-        <a:solidFill>
-          <a:schemeClr val="phClr">
-            <a:tint val="95000"/>
-            <a:satMod val="170000"/>
-          </a:schemeClr>
-        </a:solidFill>
         <a:gradFill rotWithShape="1">
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:tint val="93000"/>
-                <a:satMod val="150000"/>
-                <a:shade val="98000"/>
-                <a:lumMod val="102000"/>
+                <a:tint val="40000"/>
+                <a:satMod val="350000"/>
               </a:schemeClr>
             </a:gs>
-            <a:gs pos="50000">
+            <a:gs pos="40000">
               <a:schemeClr val="phClr">
-                <a:tint val="98000"/>
-                <a:satMod val="130000"/>
-                <a:shade val="90000"/>
-                <a:lumMod val="103000"/>
+                <a:tint val="45000"/>
+                <a:shade val="99000"/>
+                <a:satMod val="350000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:shade val="63000"/>
-                <a:satMod val="120000"/>
+                <a:tint val="20000"/>
+                <a:satMod val="255000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="5400000" scaled="0"/>
+          <a:path path="circle">
+            <a:fillToRect l="50000" t="-80000" r="50000" b="180000"/>
+          </a:path>
+        </a:gradFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:satMod val="300000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:tint val="80000"/>
+                <a:satMod val="200000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:path path="circle">
+            <a:fillToRect l="50000" t="50000" r="50000" b="50000"/>
+          </a:path>
         </a:gradFill>
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
+  <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
-    <outlinePr summaryBelow="0" summaryRight="0"/>
+    <outlinePr summaryBelow="0"/>
   </sheetPr>
-  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
+  <dimension ref="A1:AF14"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col customWidth="1" min="1" max="3" width="18.88"/>
-    <col customWidth="1" min="4" max="4" width="32.63"/>
-    <col customWidth="1" min="5" max="32" width="37.63"/>
-    <col customWidth="1" min="33" max="38" width="18.88"/>
+    <col min="1" max="1" style="6" width="18.862142857142857" customWidth="1" bestFit="1"/>
+    <col min="2" max="2" style="7" width="18.862142857142857" customWidth="1" bestFit="1"/>
+    <col min="3" max="3" style="8" width="18.862142857142857" customWidth="1" bestFit="1"/>
+    <col min="4" max="4" style="7" width="32.57642857142857" customWidth="1" bestFit="1"/>
+    <col min="5" max="5" style="7" width="37.57642857142857" customWidth="1" bestFit="1"/>
+    <col min="6" max="6" style="7" width="37.57642857142857" customWidth="1" bestFit="1"/>
+    <col min="7" max="7" style="8" width="37.57642857142857" customWidth="1" bestFit="1"/>
+    <col min="8" max="8" style="7" width="37.57642857142857" customWidth="1" bestFit="1"/>
+    <col min="9" max="9" style="7" width="37.57642857142857" customWidth="1" bestFit="1"/>
+    <col min="10" max="10" style="7" width="37.57642857142857" customWidth="1" bestFit="1"/>
+    <col min="11" max="11" style="8" width="37.57642857142857" customWidth="1" bestFit="1"/>
+    <col min="12" max="12" style="7" width="37.57642857142857" customWidth="1" bestFit="1"/>
+    <col min="13" max="13" style="7" width="37.57642857142857" customWidth="1" bestFit="1"/>
+    <col min="14" max="14" style="7" width="37.57642857142857" customWidth="1" bestFit="1"/>
+    <col min="15" max="15" style="7" width="37.57642857142857" customWidth="1" bestFit="1"/>
+    <col min="16" max="16" style="7" width="37.57642857142857" customWidth="1" bestFit="1"/>
+    <col min="17" max="17" style="7" width="37.57642857142857" customWidth="1" bestFit="1"/>
+    <col min="18" max="18" style="7" width="37.57642857142857" customWidth="1" bestFit="1"/>
+    <col min="19" max="19" style="7" width="37.57642857142857" customWidth="1" bestFit="1"/>
+    <col min="20" max="20" style="7" width="37.57642857142857" customWidth="1" bestFit="1"/>
+    <col min="21" max="21" style="7" width="37.57642857142857" customWidth="1" bestFit="1"/>
+    <col min="22" max="22" style="7" width="37.57642857142857" customWidth="1" bestFit="1"/>
+    <col min="23" max="23" style="7" width="37.57642857142857" customWidth="1" bestFit="1"/>
+    <col min="24" max="24" style="7" width="37.57642857142857" customWidth="1" bestFit="1"/>
+    <col min="25" max="25" style="7" width="37.57642857142857" customWidth="1" bestFit="1"/>
+    <col min="26" max="26" style="7" width="37.57642857142857" customWidth="1" bestFit="1"/>
+    <col min="27" max="27" style="7" width="37.57642857142857" customWidth="1" bestFit="1"/>
+    <col min="28" max="28" style="8" width="37.57642857142857" customWidth="1" bestFit="1"/>
+    <col min="29" max="29" style="7" width="37.57642857142857" customWidth="1" bestFit="1"/>
+    <col min="30" max="30" style="7" width="37.57642857142857" customWidth="1" bestFit="1"/>
+    <col min="31" max="31" style="7" width="37.57642857142857" customWidth="1" bestFit="1"/>
+    <col min="32" max="32" style="7" width="37.57642857142857" customWidth="1" bestFit="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="22.5" customHeight="1">
+    <row x14ac:dyDescent="0.25" r="1" customHeight="1" ht="22.5">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F1" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="G1" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="H1" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="I1" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="J1" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="K1" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="1" t="s">
+      <c r="L1" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="1" t="s">
+      <c r="M1" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="1" t="s">
+      <c r="N1" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="O1" s="1" t="s">
+      <c r="O1" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="P1" s="1" t="s">
+      <c r="P1" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="Q1" s="1" t="s">
+      <c r="Q1" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="R1" s="1" t="s">
+      <c r="R1" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="S1" s="1" t="s">
+      <c r="S1" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="T1" s="1" t="s">
+      <c r="T1" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="U1" s="1" t="s">
+      <c r="U1" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="V1" s="1" t="s">
+      <c r="V1" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="W1" s="1" t="s">
+      <c r="W1" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="X1" s="1" t="s">
+      <c r="X1" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="Y1" s="1" t="s">
+      <c r="Y1" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="Z1" s="1" t="s">
+      <c r="Z1" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="AA1" s="1" t="s">
+      <c r="AA1" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="AB1" s="1" t="s">
+      <c r="AB1" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="AC1" s="1" t="s">
+      <c r="AC1" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="AD1" s="1" t="s">
+      <c r="AD1" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="AE1" s="1" t="s">
+      <c r="AE1" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="AF1" s="1" t="s">
+      <c r="AF1" s="2" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="2" ht="22.5" customHeight="1">
-      <c r="A2" s="2">
-        <v>46275.63592076389</v>
-      </c>
-      <c r="B2" s="3" t="s">
+    <row x14ac:dyDescent="0.25" r="2" customHeight="1" ht="18.75">
+      <c r="A2" s="1">
+        <v>46275.635925925926</v>
+      </c>
+      <c r="B2" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="C2" s="3">
-        <v>1.0</v>
-      </c>
-      <c r="D2" s="3" t="s">
+      <c r="C2" s="4">
+        <v>1</v>
+      </c>
+      <c r="D2" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="E2" s="3" t="s">
+      <c r="E2" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="F2" s="3" t="s">
+      <c r="F2" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="G2" s="3">
-        <v>1.0</v>
-      </c>
-      <c r="H2" s="3" t="s">
+      <c r="G2" s="4">
+        <v>1</v>
+      </c>
+      <c r="H2" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="I2" s="3" t="s">
+      <c r="I2" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="J2" s="3" t="s">
+      <c r="J2" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="K2" s="3">
-        <v>2.0</v>
-      </c>
-      <c r="L2" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="M2" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="N2" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="O2" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="P2" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="Q2" s="3" t="s">
+      <c r="K2" s="4">
+        <v>2</v>
+      </c>
+      <c r="L2" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="M2" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="N2" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="O2" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="P2" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="Q2" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="R2" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="S2" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="T2" s="3" t="s">
+      <c r="R2" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="S2" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="T2" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="U2" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="V2" s="3" t="s">
+      <c r="U2" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="V2" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="W2" s="3" t="s">
+      <c r="W2" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="X2" s="3" t="s">
+      <c r="X2" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="Y2" s="3" t="s">
+      <c r="Y2" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="Z2" s="3" t="s">
+      <c r="Z2" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="AA2" s="3" t="s">
+      <c r="AA2" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="AB2" s="3">
-        <v>5.0</v>
-      </c>
-      <c r="AC2" s="3" t="s">
+      <c r="AB2" s="4">
+        <v>5</v>
+      </c>
+      <c r="AC2" s="2" t="s">
         <v>49</v>
       </c>
-      <c r="AD2" s="3" t="s">
+      <c r="AD2" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="AE2" s="3" t="s">
+      <c r="AE2" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="AF2" s="3" t="s">
+      <c r="AF2" s="2" t="s">
         <v>51</v>
       </c>
     </row>
-    <row r="3" ht="22.5" customHeight="1">
-      <c r="A3" s="4">
-        <v>46275.65241159722</v>
-      </c>
-      <c r="B3" s="5" t="s">
+    <row x14ac:dyDescent="0.25" r="3" customHeight="1" ht="18.75">
+      <c r="A3" s="1">
+        <v>46275.652407407404</v>
+      </c>
+      <c r="B3" s="2" t="s">
         <v>52</v>
       </c>
-      <c r="C3" s="5" t="s">
+      <c r="C3" s="3" t="s">
         <v>53</v>
       </c>
-      <c r="D3" s="5" t="s">
+      <c r="D3" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="E3" s="5" t="s">
+      <c r="E3" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="F3" s="5" t="s">
+      <c r="F3" s="2" t="s">
         <v>54</v>
       </c>
-      <c r="G3" s="5">
-        <v>5.0</v>
-      </c>
-      <c r="H3" s="5" t="s">
+      <c r="G3" s="4">
+        <v>5</v>
+      </c>
+      <c r="H3" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="I3" s="5" t="s">
+      <c r="I3" s="2" t="s">
         <v>56</v>
       </c>
-      <c r="J3" s="5" t="s">
+      <c r="J3" s="2" t="s">
         <v>57</v>
       </c>
-      <c r="K3" s="5">
-        <v>4.0</v>
-      </c>
-      <c r="L3" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="M3" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="N3" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="O3" s="5" t="s">
+      <c r="K3" s="4">
+        <v>4</v>
+      </c>
+      <c r="L3" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="M3" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="N3" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="O3" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="P3" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="Q3" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="R3" s="5" t="s">
+      <c r="P3" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="Q3" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="R3" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="S3" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="T3" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="U3" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="V3" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="W3" s="5" t="s">
+      <c r="S3" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="T3" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="U3" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="V3" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="W3" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="X3" s="5" t="s">
+      <c r="X3" s="2" t="s">
         <v>59</v>
       </c>
-      <c r="Y3" s="5" t="s">
+      <c r="Y3" s="2" t="s">
         <v>60</v>
       </c>
-      <c r="Z3" s="5" t="s">
+      <c r="Z3" s="2" t="s">
         <v>61</v>
       </c>
-      <c r="AA3" s="5" t="s">
+      <c r="AA3" s="2" t="s">
         <v>62</v>
       </c>
-      <c r="AB3" s="5">
-        <v>5.0</v>
-      </c>
-      <c r="AC3" s="5" t="s">
+      <c r="AB3" s="4">
+        <v>5</v>
+      </c>
+      <c r="AC3" s="2" t="s">
         <v>63</v>
       </c>
-      <c r="AD3" s="5" t="s">
+      <c r="AD3" s="2" t="s">
         <v>64</v>
       </c>
-      <c r="AE3" s="5" t="s">
+      <c r="AE3" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="AF3" s="5" t="s">
+      <c r="AF3" s="2" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="4" ht="22.5" customHeight="1">
-      <c r="A4" s="4">
-        <v>46275.73711008102</v>
-      </c>
-      <c r="B4" s="5" t="s">
+    <row x14ac:dyDescent="0.25" r="4" customHeight="1" ht="18.75">
+      <c r="A4" s="1">
+        <v>46275.73710648148</v>
+      </c>
+      <c r="B4" s="2" t="s">
         <v>66</v>
       </c>
-      <c r="C4" s="5">
-        <v>7.0</v>
-      </c>
-      <c r="D4" s="5" t="s">
+      <c r="C4" s="4">
+        <v>7</v>
+      </c>
+      <c r="D4" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="E4" s="5" t="s">
+      <c r="E4" s="2" t="s">
         <v>67</v>
       </c>
-      <c r="F4" s="5" t="s">
+      <c r="F4" s="2" t="s">
         <v>54</v>
       </c>
-      <c r="G4" s="5">
-        <v>4.0</v>
-      </c>
-      <c r="H4" s="5" t="s">
+      <c r="G4" s="4">
+        <v>4</v>
+      </c>
+      <c r="H4" s="2" t="s">
         <v>68</v>
       </c>
-      <c r="I4" s="5" t="s">
+      <c r="I4" s="2" t="s">
         <v>56</v>
       </c>
-      <c r="J4" s="5" t="s">
+      <c r="J4" s="2" t="s">
         <v>69</v>
       </c>
-      <c r="K4" s="5">
-        <v>4.0</v>
-      </c>
-      <c r="L4" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="M4" s="5" t="s">
+      <c r="K4" s="4">
+        <v>4</v>
+      </c>
+      <c r="L4" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="M4" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="N4" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="O4" s="5" t="s">
+      <c r="N4" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="O4" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="P4" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="Q4" s="5" t="s">
+      <c r="P4" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="Q4" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="R4" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="S4" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="T4" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="U4" s="5" t="s">
+      <c r="R4" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="S4" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="T4" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="U4" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="V4" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="W4" s="5" t="s">
+      <c r="V4" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="W4" s="2" t="s">
         <v>70</v>
       </c>
-      <c r="X4" s="5" t="s">
+      <c r="X4" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="Y4" s="5" t="s">
+      <c r="Y4" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="Z4" s="5" t="s">
+      <c r="Z4" s="2" t="s">
         <v>61</v>
       </c>
-      <c r="AA4" s="5" t="s">
+      <c r="AA4" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="AB4" s="5">
-        <v>4.0</v>
-      </c>
-      <c r="AC4" s="5" t="s">
+      <c r="AB4" s="4">
+        <v>4</v>
+      </c>
+      <c r="AC4" s="2" t="s">
         <v>71</v>
       </c>
-      <c r="AD4" s="5" t="s">
+      <c r="AD4" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="AE4" s="5" t="s">
+      <c r="AE4" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="AF4" s="5" t="s">
+      <c r="AF4" s="2" t="s">
         <v>72</v>
       </c>
     </row>
-    <row r="5" ht="22.5" customHeight="1">
-      <c r="A5" s="4">
-        <v>46275.742181608795</v>
-      </c>
-      <c r="B5" s="5" t="s">
+    <row x14ac:dyDescent="0.25" r="5" customHeight="1" ht="18.75">
+      <c r="A5" s="1">
+        <v>46275.74217592592</v>
+      </c>
+      <c r="B5" s="2" t="s">
         <v>73</v>
       </c>
-      <c r="C5" s="5">
-        <v>7.0</v>
-      </c>
-      <c r="D5" s="5" t="s">
+      <c r="C5" s="4">
+        <v>7</v>
+      </c>
+      <c r="D5" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="E5" s="5" t="s">
+      <c r="E5" s="2" t="s">
         <v>67</v>
       </c>
-      <c r="F5" s="5" t="s">
+      <c r="F5" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="G5" s="5">
-        <v>3.0</v>
-      </c>
-      <c r="H5" s="5" t="s">
+      <c r="G5" s="4">
+        <v>3</v>
+      </c>
+      <c r="H5" s="2" t="s">
         <v>75</v>
       </c>
-      <c r="I5" s="5" t="s">
+      <c r="I5" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="J5" s="5" t="s">
+      <c r="J5" s="2" t="s">
         <v>69</v>
       </c>
-      <c r="K5" s="5">
-        <v>3.0</v>
-      </c>
-      <c r="L5" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="M5" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="N5" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="O5" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="P5" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="Q5" s="5" t="s">
+      <c r="K5" s="4">
+        <v>3</v>
+      </c>
+      <c r="L5" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="M5" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="N5" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="O5" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="P5" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="Q5" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="R5" s="5" t="s">
+      <c r="R5" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="S5" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="T5" s="5" t="s">
+      <c r="S5" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="T5" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="U5" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="V5" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="W5" s="5" t="s">
+      <c r="U5" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="V5" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="W5" s="2" t="s">
         <v>76</v>
       </c>
-      <c r="X5" s="5" t="s">
+      <c r="X5" s="2" t="s">
         <v>77</v>
       </c>
-      <c r="Y5" s="5" t="s">
+      <c r="Y5" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="Z5" s="5" t="s">
+      <c r="Z5" s="2" t="s">
         <v>61</v>
       </c>
-      <c r="AA5" s="5" t="s">
+      <c r="AA5" s="2" t="s">
         <v>78</v>
       </c>
-      <c r="AB5" s="5">
-        <v>4.0</v>
-      </c>
-      <c r="AC5" s="5" t="s">
+      <c r="AB5" s="4">
+        <v>4</v>
+      </c>
+      <c r="AC5" s="2" t="s">
         <v>79</v>
       </c>
-      <c r="AD5" s="5" t="s">
+      <c r="AD5" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="AE5" s="5" t="s">
+      <c r="AE5" s="2" t="s">
         <v>80</v>
       </c>
+      <c r="AF5" s="5"/>
     </row>
-    <row r="6" ht="22.5" customHeight="1">
-      <c r="A6" s="4">
-        <v>46275.89641984954</v>
-      </c>
-      <c r="B6" s="5" t="s">
+    <row x14ac:dyDescent="0.25" r="6" customHeight="1" ht="18.75">
+      <c r="A6" s="1">
+        <v>46275.89642361111</v>
+      </c>
+      <c r="B6" s="2" t="s">
         <v>81</v>
       </c>
-      <c r="C6" s="5">
-        <v>5.0</v>
-      </c>
-      <c r="D6" s="5" t="s">
+      <c r="C6" s="4">
+        <v>5</v>
+      </c>
+      <c r="D6" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="E6" s="5" t="s">
+      <c r="E6" s="2" t="s">
         <v>67</v>
       </c>
-      <c r="F6" s="5" t="s">
+      <c r="F6" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="G6" s="5">
-        <v>5.0</v>
-      </c>
-      <c r="H6" s="5" t="s">
+      <c r="G6" s="4">
+        <v>5</v>
+      </c>
+      <c r="H6" s="2" t="s">
         <v>82</v>
       </c>
-      <c r="I6" s="5" t="s">
+      <c r="I6" s="2" t="s">
         <v>83</v>
       </c>
-      <c r="J6" s="5" t="s">
+      <c r="J6" s="2" t="s">
         <v>57</v>
       </c>
-      <c r="K6" s="5">
-        <v>5.0</v>
-      </c>
-      <c r="L6" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="M6" s="5" t="s">
+      <c r="K6" s="4">
+        <v>5</v>
+      </c>
+      <c r="L6" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="M6" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="N6" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="O6" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="P6" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="Q6" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="R6" s="5" t="s">
+      <c r="N6" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="O6" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="P6" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="Q6" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="R6" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="S6" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="T6" s="5" t="s">
+      <c r="S6" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="T6" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="U6" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="V6" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="W6" s="5" t="s">
+      <c r="U6" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="V6" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="W6" s="2" t="s">
         <v>84</v>
       </c>
-      <c r="X6" s="5" t="s">
+      <c r="X6" s="2" t="s">
         <v>59</v>
       </c>
-      <c r="Y6" s="5" t="s">
+      <c r="Y6" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="Z6" s="5" t="s">
+      <c r="Z6" s="2" t="s">
         <v>61</v>
       </c>
-      <c r="AA6" s="5" t="s">
+      <c r="AA6" s="2" t="s">
         <v>85</v>
       </c>
-      <c r="AB6" s="5">
-        <v>4.0</v>
-      </c>
-      <c r="AC6" s="5" t="s">
+      <c r="AB6" s="4">
+        <v>4</v>
+      </c>
+      <c r="AC6" s="2" t="s">
         <v>86</v>
       </c>
-      <c r="AD6" s="5" t="s">
+      <c r="AD6" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="AE6" s="5" t="s">
+      <c r="AE6" s="2" t="s">
         <v>87</v>
       </c>
-      <c r="AF6" s="5" t="s">
+      <c r="AF6" s="2" t="s">
         <v>88</v>
       </c>
     </row>
-    <row r="7" ht="22.5" customHeight="1">
-      <c r="A7" s="4">
-        <v>46275.929298483796</v>
-      </c>
-      <c r="B7" s="5" t="s">
+    <row x14ac:dyDescent="0.25" r="7" customHeight="1" ht="18.75">
+      <c r="A7" s="1">
+        <v>46275.929293981484</v>
+      </c>
+      <c r="B7" s="2" t="s">
         <v>89</v>
       </c>
-      <c r="C7" s="5">
-        <v>8.0</v>
-      </c>
-      <c r="D7" s="5" t="s">
+      <c r="C7" s="4">
+        <v>8</v>
+      </c>
+      <c r="D7" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="E7" s="5" t="s">
+      <c r="E7" s="2" t="s">
         <v>90</v>
       </c>
-      <c r="F7" s="5" t="s">
+      <c r="F7" s="2" t="s">
         <v>54</v>
       </c>
-      <c r="G7" s="5">
-        <v>5.0</v>
-      </c>
-      <c r="H7" s="5" t="s">
+      <c r="G7" s="4">
+        <v>5</v>
+      </c>
+      <c r="H7" s="2" t="s">
         <v>91</v>
       </c>
-      <c r="I7" s="5" t="s">
+      <c r="I7" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="J7" s="5" t="s">
+      <c r="J7" s="2" t="s">
         <v>92</v>
       </c>
-      <c r="K7" s="5">
-        <v>2.0</v>
-      </c>
-      <c r="L7" s="5" t="s">
+      <c r="K7" s="4">
+        <v>2</v>
+      </c>
+      <c r="L7" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="M7" s="5" t="s">
+      <c r="M7" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="N7" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="O7" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="P7" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="Q7" s="5" t="s">
+      <c r="N7" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="O7" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="P7" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="Q7" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="R7" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="S7" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="T7" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="U7" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="V7" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="W7" s="5" t="s">
+      <c r="R7" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="S7" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="T7" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="U7" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="V7" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="W7" s="2" t="s">
         <v>93</v>
       </c>
-      <c r="X7" s="5" t="s">
+      <c r="X7" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="Y7" s="5" t="s">
+      <c r="Y7" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="Z7" s="5" t="s">
+      <c r="Z7" s="2" t="s">
         <v>94</v>
       </c>
-      <c r="AA7" s="5" t="s">
+      <c r="AA7" s="2" t="s">
         <v>95</v>
       </c>
-      <c r="AB7" s="5">
-        <v>3.0</v>
-      </c>
-      <c r="AC7" s="5" t="s">
+      <c r="AB7" s="4">
+        <v>3</v>
+      </c>
+      <c r="AC7" s="2" t="s">
         <v>96</v>
       </c>
-      <c r="AD7" s="5" t="s">
+      <c r="AD7" s="2" t="s">
         <v>64</v>
       </c>
-      <c r="AE7" s="5" t="s">
+      <c r="AE7" s="2" t="s">
         <v>87</v>
       </c>
+      <c r="AF7" s="5"/>
     </row>
-    <row r="8" ht="22.5" customHeight="1">
-      <c r="A8" s="4">
-        <v>46275.932893958336</v>
-      </c>
-      <c r="B8" s="5" t="s">
+    <row x14ac:dyDescent="0.25" r="8" customHeight="1" ht="18.75">
+      <c r="A8" s="1">
+        <v>46275.93289351852</v>
+      </c>
+      <c r="B8" s="2" t="s">
         <v>97</v>
       </c>
-      <c r="C8" s="5" t="s">
+      <c r="C8" s="3" t="s">
         <v>98</v>
       </c>
-      <c r="D8" s="5" t="s">
+      <c r="D8" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="E8" s="5" t="s">
+      <c r="E8" s="2" t="s">
         <v>90</v>
       </c>
-      <c r="F8" s="5" t="s">
+      <c r="F8" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="G8" s="5">
-        <v>4.0</v>
-      </c>
-      <c r="H8" s="5" t="s">
+      <c r="G8" s="4">
+        <v>4</v>
+      </c>
+      <c r="H8" s="2" t="s">
         <v>99</v>
       </c>
-      <c r="I8" s="5" t="s">
+      <c r="I8" s="2" t="s">
         <v>56</v>
       </c>
-      <c r="J8" s="5" t="s">
+      <c r="J8" s="2" t="s">
         <v>57</v>
       </c>
-      <c r="K8" s="5">
-        <v>3.0</v>
-      </c>
-      <c r="L8" s="5" t="s">
+      <c r="K8" s="4">
+        <v>3</v>
+      </c>
+      <c r="L8" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="M8" s="5" t="s">
+      <c r="M8" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="N8" s="5" t="s">
+      <c r="N8" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="O8" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="P8" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="Q8" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="R8" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="S8" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="T8" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="U8" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="V8" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="W8" s="5" t="s">
+      <c r="O8" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="P8" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="Q8" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="R8" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="S8" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="T8" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="U8" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="V8" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="W8" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="X8" s="5" t="s">
+      <c r="X8" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="Y8" s="5" t="s">
+      <c r="Y8" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="Z8" s="5" t="s">
+      <c r="Z8" s="2" t="s">
         <v>94</v>
       </c>
-      <c r="AA8" s="5" t="s">
+      <c r="AA8" s="2" t="s">
         <v>100</v>
       </c>
-      <c r="AB8" s="5">
-        <v>4.0</v>
-      </c>
-      <c r="AC8" s="5" t="s">
+      <c r="AB8" s="4">
+        <v>4</v>
+      </c>
+      <c r="AC8" s="2" t="s">
         <v>101</v>
       </c>
-      <c r="AD8" s="5" t="s">
+      <c r="AD8" s="2" t="s">
         <v>64</v>
       </c>
-      <c r="AE8" s="5" t="s">
+      <c r="AE8" s="2" t="s">
         <v>50</v>
       </c>
+      <c r="AF8" s="5"/>
     </row>
-    <row r="9" ht="22.5" customHeight="1">
-      <c r="A9" s="4">
-        <v>46275.947633715274</v>
-      </c>
-      <c r="B9" s="5" t="s">
+    <row x14ac:dyDescent="0.25" r="9" customHeight="1" ht="18.75">
+      <c r="A9" s="1">
+        <v>46275.94763888889</v>
+      </c>
+      <c r="B9" s="2" t="s">
         <v>102</v>
       </c>
-      <c r="C9" s="5">
-        <v>8.0</v>
-      </c>
-      <c r="D9" s="5" t="s">
+      <c r="C9" s="4">
+        <v>8</v>
+      </c>
+      <c r="D9" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="E9" s="5" t="s">
+      <c r="E9" s="2" t="s">
         <v>90</v>
       </c>
-      <c r="F9" s="5" t="s">
+      <c r="F9" s="2" t="s">
         <v>54</v>
       </c>
-      <c r="G9" s="5">
-        <v>2.0</v>
-      </c>
-      <c r="H9" s="5" t="s">
+      <c r="G9" s="4">
+        <v>2</v>
+      </c>
+      <c r="H9" s="2" t="s">
         <v>103</v>
       </c>
-      <c r="I9" s="5" t="s">
+      <c r="I9" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="J9" s="5" t="s">
+      <c r="J9" s="2" t="s">
         <v>104</v>
       </c>
-      <c r="K9" s="5">
-        <v>3.0</v>
-      </c>
-      <c r="L9" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="M9" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="N9" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="O9" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="P9" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="Q9" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="R9" s="5" t="s">
+      <c r="K9" s="4">
+        <v>3</v>
+      </c>
+      <c r="L9" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="M9" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="N9" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="O9" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="P9" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="Q9" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="R9" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="S9" s="5" t="s">
+      <c r="S9" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="T9" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="U9" s="5" t="s">
+      <c r="T9" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="U9" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="V9" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="W9" s="5" t="s">
+      <c r="V9" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="W9" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="X9" s="5" t="s">
+      <c r="X9" s="2" t="s">
         <v>59</v>
       </c>
-      <c r="Y9" s="5" t="s">
+      <c r="Y9" s="2" t="s">
         <v>60</v>
       </c>
-      <c r="Z9" s="5" t="s">
+      <c r="Z9" s="2" t="s">
         <v>105</v>
       </c>
-      <c r="AA9" s="5" t="s">
+      <c r="AA9" s="2" t="s">
         <v>95</v>
       </c>
-      <c r="AB9" s="5">
-        <v>3.0</v>
-      </c>
-      <c r="AC9" s="5" t="s">
+      <c r="AB9" s="4">
+        <v>3</v>
+      </c>
+      <c r="AC9" s="2" t="s">
         <v>96</v>
       </c>
-      <c r="AD9" s="5" t="s">
+      <c r="AD9" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="AE9" s="5" t="s">
+      <c r="AE9" s="2" t="s">
         <v>50</v>
       </c>
+      <c r="AF9" s="5"/>
     </row>
-    <row r="10" ht="22.5" customHeight="1">
-      <c r="A10" s="4">
-        <v>46276.00633905093</v>
-      </c>
-      <c r="B10" s="5" t="s">
+    <row x14ac:dyDescent="0.25" r="10" customHeight="1" ht="18.75">
+      <c r="A10" s="1">
+        <v>46276.00634259259</v>
+      </c>
+      <c r="B10" s="2" t="s">
         <v>106</v>
       </c>
-      <c r="C10" s="5">
-        <v>2.0</v>
-      </c>
-      <c r="D10" s="5" t="s">
+      <c r="C10" s="4">
+        <v>2</v>
+      </c>
+      <c r="D10" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="E10" s="5" t="s">
+      <c r="E10" s="2" t="s">
         <v>67</v>
       </c>
-      <c r="F10" s="5" t="s">
+      <c r="F10" s="2" t="s">
         <v>54</v>
       </c>
-      <c r="G10" s="5">
-        <v>4.0</v>
-      </c>
-      <c r="H10" s="5" t="s">
+      <c r="G10" s="4">
+        <v>4</v>
+      </c>
+      <c r="H10" s="2" t="s">
         <v>107</v>
       </c>
-      <c r="I10" s="5" t="s">
+      <c r="I10" s="2" t="s">
         <v>56</v>
       </c>
-      <c r="J10" s="5" t="s">
+      <c r="J10" s="2" t="s">
         <v>69</v>
       </c>
-      <c r="K10" s="5">
-        <v>4.0</v>
-      </c>
-      <c r="L10" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="M10" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="N10" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="O10" s="5" t="s">
+      <c r="K10" s="4">
+        <v>4</v>
+      </c>
+      <c r="L10" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="M10" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="N10" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="O10" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="P10" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="Q10" s="5" t="s">
+      <c r="P10" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="Q10" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="R10" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="S10" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="T10" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="U10" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="V10" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="W10" s="5" t="s">
+      <c r="R10" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="S10" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="T10" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="U10" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="V10" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="W10" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="X10" s="5" t="s">
+      <c r="X10" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="Y10" s="5" t="s">
+      <c r="Y10" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="Z10" s="5" t="s">
+      <c r="Z10" s="2" t="s">
         <v>108</v>
       </c>
-      <c r="AA10" s="5" t="s">
+      <c r="AA10" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="AB10" s="5">
-        <v>5.0</v>
-      </c>
-      <c r="AC10" s="5" t="s">
+      <c r="AB10" s="4">
+        <v>5</v>
+      </c>
+      <c r="AC10" s="2" t="s">
         <v>109</v>
       </c>
-      <c r="AD10" s="5" t="s">
+      <c r="AD10" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="AE10" s="5" t="s">
+      <c r="AE10" s="2" t="s">
         <v>80</v>
       </c>
-      <c r="AF10" s="5" t="s">
+      <c r="AF10" s="2" t="s">
         <v>88</v>
       </c>
     </row>
-    <row r="11" ht="22.5" customHeight="1">
-      <c r="A11" s="4">
-        <v>46276.237369305556</v>
-      </c>
-      <c r="B11" s="5" t="s">
+    <row x14ac:dyDescent="0.25" r="11" customHeight="1" ht="18.75">
+      <c r="A11" s="1">
+        <v>46276.23737268519</v>
+      </c>
+      <c r="B11" s="2" t="s">
         <v>110</v>
       </c>
-      <c r="C11" s="5">
-        <v>7.0</v>
-      </c>
-      <c r="D11" s="5" t="s">
+      <c r="C11" s="4">
+        <v>7</v>
+      </c>
+      <c r="D11" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="E11" s="5" t="s">
+      <c r="E11" s="2" t="s">
         <v>90</v>
       </c>
-      <c r="F11" s="5" t="s">
+      <c r="F11" s="2" t="s">
         <v>54</v>
       </c>
-      <c r="G11" s="5">
-        <v>4.0</v>
-      </c>
-      <c r="H11" s="5" t="s">
+      <c r="G11" s="4">
+        <v>4</v>
+      </c>
+      <c r="H11" s="2" t="s">
         <v>111</v>
       </c>
-      <c r="I11" s="5" t="s">
+      <c r="I11" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="J11" s="5" t="s">
+      <c r="J11" s="2" t="s">
         <v>112</v>
       </c>
-      <c r="K11" s="5">
-        <v>4.0</v>
-      </c>
-      <c r="L11" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="M11" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="N11" s="5" t="s">
+      <c r="K11" s="4">
+        <v>4</v>
+      </c>
+      <c r="L11" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="M11" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="N11" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="O11" s="5" t="s">
+      <c r="O11" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="P11" s="5" t="s">
+      <c r="P11" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="Q11" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="R11" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="S11" s="5" t="s">
+      <c r="Q11" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="R11" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="S11" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="T11" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="U11" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="V11" s="5" t="s">
+      <c r="T11" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="U11" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="V11" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="W11" s="5" t="s">
+      <c r="W11" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="X11" s="5" t="s">
+      <c r="X11" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="Y11" s="5" t="s">
+      <c r="Y11" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="Z11" s="5" t="s">
+      <c r="Z11" s="2" t="s">
         <v>61</v>
       </c>
-      <c r="AA11" s="5" t="s">
+      <c r="AA11" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="AB11" s="5">
-        <v>5.0</v>
-      </c>
-      <c r="AC11" s="5" t="s">
+      <c r="AB11" s="4">
+        <v>5</v>
+      </c>
+      <c r="AC11" s="2" t="s">
         <v>101</v>
       </c>
-      <c r="AD11" s="5" t="s">
+      <c r="AD11" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="AE11" s="5" t="s">
+      <c r="AE11" s="2" t="s">
         <v>80</v>
       </c>
+      <c r="AF11" s="5"/>
     </row>
-    <row r="12" ht="22.5" customHeight="1">
-      <c r="A12" s="4">
-        <v>46276.44918925926</v>
-      </c>
-      <c r="B12" s="5" t="s">
+    <row x14ac:dyDescent="0.25" r="12" customHeight="1" ht="18.75">
+      <c r="A12" s="1">
+        <v>46276.44918981481</v>
+      </c>
+      <c r="B12" s="2" t="s">
         <v>113</v>
       </c>
-      <c r="C12" s="5">
-        <v>7.0</v>
-      </c>
-      <c r="D12" s="5" t="s">
+      <c r="C12" s="4">
+        <v>7</v>
+      </c>
+      <c r="D12" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="E12" s="5" t="s">
+      <c r="E12" s="2" t="s">
         <v>114</v>
       </c>
-      <c r="F12" s="5" t="s">
+      <c r="F12" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="G12" s="5">
-        <v>5.0</v>
-      </c>
-      <c r="H12" s="5" t="s">
+      <c r="G12" s="4">
+        <v>5</v>
+      </c>
+      <c r="H12" s="2" t="s">
         <v>115</v>
       </c>
-      <c r="I12" s="5" t="s">
+      <c r="I12" s="2" t="s">
         <v>83</v>
       </c>
-      <c r="J12" s="5" t="s">
+      <c r="J12" s="2" t="s">
         <v>57</v>
       </c>
-      <c r="K12" s="5">
-        <v>3.0</v>
-      </c>
-      <c r="L12" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="M12" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="N12" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="O12" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="P12" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="Q12" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="R12" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="S12" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="T12" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="U12" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="V12" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="W12" s="5" t="s">
+      <c r="K12" s="4">
+        <v>3</v>
+      </c>
+      <c r="L12" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="M12" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="N12" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="O12" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="P12" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="Q12" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="R12" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="S12" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="T12" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="U12" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="V12" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="W12" s="2" t="s">
         <v>116</v>
       </c>
-      <c r="X12" s="5" t="s">
+      <c r="X12" s="2" t="s">
         <v>59</v>
       </c>
-      <c r="Y12" s="5" t="s">
+      <c r="Y12" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="Z12" s="5" t="s">
+      <c r="Z12" s="2" t="s">
         <v>117</v>
       </c>
-      <c r="AA12" s="5" t="s">
+      <c r="AA12" s="2" t="s">
         <v>85</v>
       </c>
-      <c r="AB12" s="5">
-        <v>5.0</v>
-      </c>
-      <c r="AC12" s="5" t="s">
+      <c r="AB12" s="4">
+        <v>5</v>
+      </c>
+      <c r="AC12" s="2" t="s">
         <v>118</v>
       </c>
-      <c r="AD12" s="5" t="s">
+      <c r="AD12" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="AE12" s="5" t="s">
+      <c r="AE12" s="2" t="s">
         <v>50</v>
       </c>
+      <c r="AF12" s="5"/>
     </row>
-    <row r="13" ht="22.5" customHeight="1">
-      <c r="A13" s="4">
-        <v>46276.63761604167</v>
-      </c>
-      <c r="B13" s="5" t="s">
+    <row x14ac:dyDescent="0.25" r="13" customHeight="1" ht="18.75">
+      <c r="A13" s="1">
+        <v>46276.63761574074</v>
+      </c>
+      <c r="B13" s="2" t="s">
         <v>119</v>
       </c>
-      <c r="C13" s="5">
-        <v>6.0</v>
-      </c>
-      <c r="D13" s="5" t="s">
+      <c r="C13" s="4">
+        <v>6</v>
+      </c>
+      <c r="D13" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="E13" s="5" t="s">
+      <c r="E13" s="2" t="s">
         <v>67</v>
       </c>
-      <c r="F13" s="5" t="s">
+      <c r="F13" s="2" t="s">
         <v>120</v>
       </c>
-      <c r="G13" s="5">
-        <v>1.0</v>
-      </c>
-      <c r="H13" s="5" t="s">
+      <c r="G13" s="4">
+        <v>1</v>
+      </c>
+      <c r="H13" s="2" t="s">
         <v>121</v>
       </c>
-      <c r="I13" s="5" t="s">
+      <c r="I13" s="2" t="s">
         <v>56</v>
       </c>
-      <c r="J13" s="5" t="s">
+      <c r="J13" s="2" t="s">
         <v>112</v>
       </c>
-      <c r="K13" s="5">
-        <v>4.0</v>
-      </c>
-      <c r="L13" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="M13" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="N13" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="O13" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="P13" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="Q13" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="R13" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="S13" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="T13" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="U13" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="V13" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="W13" s="5" t="s">
+      <c r="K13" s="4">
+        <v>4</v>
+      </c>
+      <c r="L13" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="M13" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="N13" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="O13" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="P13" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="Q13" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="R13" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="S13" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="T13" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="U13" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="V13" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="W13" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="X13" s="5" t="s">
+      <c r="X13" s="2" t="s">
         <v>59</v>
       </c>
-      <c r="Y13" s="5" t="s">
+      <c r="Y13" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="Z13" s="5" t="s">
+      <c r="Z13" s="2" t="s">
         <v>61</v>
       </c>
-      <c r="AA13" s="5" t="s">
+      <c r="AA13" s="2" t="s">
         <v>122</v>
       </c>
-      <c r="AB13" s="5">
-        <v>5.0</v>
-      </c>
-      <c r="AC13" s="5" t="s">
+      <c r="AB13" s="4">
+        <v>5</v>
+      </c>
+      <c r="AC13" s="2" t="s">
         <v>101</v>
       </c>
-      <c r="AD13" s="5" t="s">
+      <c r="AD13" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="AE13" s="5" t="s">
+      <c r="AE13" s="2" t="s">
         <v>87</v>
       </c>
+      <c r="AF13" s="5"/>
     </row>
-    <row r="14" ht="22.5" customHeight="1">
-      <c r="A14" s="4">
-        <v>46277.5338525463</v>
-      </c>
-      <c r="B14" s="5" t="s">
+    <row x14ac:dyDescent="0.25" r="14" customHeight="1" ht="18.75">
+      <c r="A14" s="1">
+        <v>46277.533854166664</v>
+      </c>
+      <c r="B14" s="2" t="s">
         <v>123</v>
       </c>
-      <c r="C14" s="5">
-        <v>5.0</v>
-      </c>
-      <c r="D14" s="5" t="s">
+      <c r="C14" s="4">
+        <v>5</v>
+      </c>
+      <c r="D14" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="E14" s="5" t="s">
+      <c r="E14" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="F14" s="5" t="s">
+      <c r="F14" s="2" t="s">
         <v>54</v>
       </c>
-      <c r="G14" s="5">
-        <v>5.0</v>
-      </c>
-      <c r="H14" s="5" t="s">
+      <c r="G14" s="4">
+        <v>5</v>
+      </c>
+      <c r="H14" s="2" t="s">
         <v>103</v>
       </c>
-      <c r="I14" s="5" t="s">
+      <c r="I14" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="J14" s="5" t="s">
+      <c r="J14" s="2" t="s">
         <v>57</v>
       </c>
-      <c r="K14" s="5">
-        <v>4.0</v>
-      </c>
-      <c r="L14" s="5" t="s">
+      <c r="K14" s="4">
+        <v>4</v>
+      </c>
+      <c r="L14" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="M14" s="5" t="s">
+      <c r="M14" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="N14" s="5" t="s">
+      <c r="N14" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="O14" s="5" t="s">
+      <c r="O14" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="P14" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="Q14" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="R14" s="5" t="s">
+      <c r="P14" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="Q14" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="R14" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="S14" s="5" t="s">
+      <c r="S14" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="T14" s="5" t="s">
+      <c r="T14" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="U14" s="5" t="s">
+      <c r="U14" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="V14" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="W14" s="5" t="s">
+      <c r="V14" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="W14" s="2" t="s">
         <v>124</v>
       </c>
-      <c r="X14" s="5" t="s">
+      <c r="X14" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="Y14" s="5" t="s">
+      <c r="Y14" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="Z14" s="5" t="s">
+      <c r="Z14" s="2" t="s">
         <v>61</v>
       </c>
-      <c r="AA14" s="5" t="s">
+      <c r="AA14" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="AB14" s="5">
-        <v>5.0</v>
-      </c>
-      <c r="AC14" s="5" t="s">
+      <c r="AB14" s="4">
+        <v>5</v>
+      </c>
+      <c r="AC14" s="2" t="s">
         <v>125</v>
       </c>
-      <c r="AD14" s="5" t="s">
+      <c r="AD14" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="AE14" s="5" t="s">
+      <c r="AE14" s="2" t="s">
         <v>50</v>
       </c>
+      <c r="AF14" s="5"/>
     </row>
   </sheetData>
-  <drawing r:id="rId1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <tableParts count="1">
-    <tablePart r:id="rId3"/>
+    <tablePart r:id="rId1"/>
   </tableParts>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
-    <outlinePr summaryBelow="0" summaryRight="0"/>
+    <outlinePr summaryBelow="0"/>
   </sheetPr>
-  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData/>
-  <drawing r:id="rId1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>